--- a/input/PL/reg_fertility.xlsx
+++ b/input/PL/reg_fertility.xlsx
@@ -15,241 +15,187 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="83" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="108" uniqueCount="57">
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Authors:</t>
+  </si>
+  <si>
+    <t>Last edit:</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Process:</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>Modelparametersgoverningproje</t>
+  </si>
+  <si>
+    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
+  </si>
+  <si>
+    <t>12 Jan 2016 AB</t>
+  </si>
   <si>
     <t>Description:</t>
   </si>
   <si>
-    <t>Model parameters governing projection of fertility</t>
-  </si>
-  <si>
-    <t>Authors:</t>
-  </si>
-  <si>
-    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
-  </si>
-  <si>
-    <t>Last edit:</t>
-  </si>
-  <si>
-    <t>12 Jan 2016 AB</t>
-  </si>
-  <si>
-    <t>Process:</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
     <t>Probit regression estimates of the probability of having a child for women</t>
   </si>
   <si>
-    <t>Notes:</t>
-  </si>
-  <si>
     <t>Regions: PL4 = Polnocno-Zachodni, PL5 = Poludniowo-Zachodni, PL6 = Polnocy, PL10 = Central + East. Poludniowy is the omitted category.</t>
   </si>
   <si>
-    <t>Goodness of fit</t>
+    <t>Goodnessoffit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F1 - Fertility </t>
+  </si>
+  <si>
+    <t>Pseudo R-squared</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Chi^2</t>
+  </si>
+  <si>
+    <t>Log likelihood</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
   <si>
     <t>REGRESSOR</t>
   </si>
   <si>
+    <t>Ded</t>
+  </si>
+  <si>
+    <t>Dag</t>
+  </si>
+  <si>
+    <t>Dag_sq</t>
+  </si>
+  <si>
+    <t>Dhe_Fair</t>
+  </si>
+  <si>
+    <t>Dhe_Good</t>
+  </si>
+  <si>
+    <t>Dhe_VeryGood</t>
+  </si>
+  <si>
+    <t>Dhe_Excellent</t>
+  </si>
+  <si>
+    <t>Dcpst_Single</t>
+  </si>
+  <si>
+    <t>Dcpst_Single_L1</t>
+  </si>
+  <si>
+    <t>Ded_Dag</t>
+  </si>
+  <si>
+    <t>Ded_Dcpst_Single</t>
+  </si>
+  <si>
+    <t>Ded_Dcpst_Single_L1</t>
+  </si>
+  <si>
+    <t>Ded_Dhe_VeryGood</t>
+  </si>
+  <si>
+    <t>Ydses_c5_Q2_L1</t>
+  </si>
+  <si>
+    <t>Ydses_c5_Q3_L1</t>
+  </si>
+  <si>
+    <t>Ydses_c5_Q4_L1</t>
+  </si>
+  <si>
+    <t>Ydses_c5_Q5_L1</t>
+  </si>
+  <si>
+    <t>Dnc_L1</t>
+  </si>
+  <si>
+    <t>Dnc02_L1</t>
+  </si>
+  <si>
+    <t>Deh_c4_Low</t>
+  </si>
+  <si>
+    <t>Deh_c4_High</t>
+  </si>
+  <si>
+    <t>FertilityRate</t>
+  </si>
+  <si>
+    <t>Les_c3_Student_L1</t>
+  </si>
+  <si>
+    <t>Les_c3_NotEmployed_L1</t>
+  </si>
+  <si>
+    <t>Year_transformed</t>
+  </si>
+  <si>
+    <t>Year_transformed_sq</t>
+  </si>
+  <si>
+    <t>PL4</t>
+  </si>
+  <si>
+    <t>PL5</t>
+  </si>
+  <si>
+    <t>PL6</t>
+  </si>
+  <si>
+    <t>PL10</t>
+  </si>
+  <si>
+    <t>Constant</t>
+  </si>
+  <si>
     <t>COEFFICIENT</t>
-  </si>
-  <si>
-    <t>Ded</t>
-  </si>
-  <si>
-    <t>Dag</t>
-  </si>
-  <si>
-    <t>Dag_sq</t>
-  </si>
-  <si>
-    <t>Dhe_Fair</t>
-  </si>
-  <si>
-    <t>Dhe_Good</t>
-  </si>
-  <si>
-    <t>Dhe_VeryGood</t>
-  </si>
-  <si>
-    <t>Dhe_Excellent</t>
-  </si>
-  <si>
-    <t>Dcpst_Single</t>
-  </si>
-  <si>
-    <t>Dcpst_Single_L1</t>
-  </si>
-  <si>
-    <t>Ded_Dag</t>
-  </si>
-  <si>
-    <t>Ded_Dcpst_Single</t>
-  </si>
-  <si>
-    <t>Ded_Dcpst_Single_L1</t>
-  </si>
-  <si>
-    <t>Ded_Dhe_VeryGood</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q2_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q3_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q4_L1</t>
-  </si>
-  <si>
-    <t>Ydses_c5_Q5_L1</t>
-  </si>
-  <si>
-    <t>Dnc_L1</t>
-  </si>
-  <si>
-    <t>Dnc02_L1</t>
-  </si>
-  <si>
-    <t>Deh_c4_Low</t>
-  </si>
-  <si>
-    <t>Deh_c4_High</t>
-  </si>
-  <si>
-    <t>FertilityRate</t>
-  </si>
-  <si>
-    <t>Les_c3_Student_L1</t>
-  </si>
-  <si>
-    <t>Les_c3_NotEmployed_L1</t>
-  </si>
-  <si>
-    <t>Year_transformed</t>
-  </si>
-  <si>
-    <t>Year_transformed_sq</t>
-  </si>
-  <si>
-    <t>PL4</t>
-  </si>
-  <si>
-    <t>PL5</t>
-  </si>
-  <si>
-    <t>PL6</t>
-  </si>
-  <si>
-    <t>PL10</t>
-  </si>
-  <si>
-    <t>Constant</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve">F1 - Fertility </t>
-  </si>
-  <si>
-    <t>Pseudo R-squared</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Chi^2</t>
-  </si>
-  <si>
-    <t>Log likelihood</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="17">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -260,7 +206,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -268,100 +214,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -375,51 +235,67 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>0</v>
+      <c r="B5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
+      <c r="A8" t="s">
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -432,40 +308,162 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
-        <v>11</v>
-      </c>
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>46</v>
-      </c>
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1">
         <v>0.18837218489777297</v>
       </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
       <c r="E11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11">
+        <v>21</v>
+      </c>
+      <c r="F11" s="1">
         <v>900.27293767677497</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1">
         <v>55355</v>
       </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
       <c r="E12" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12">
+        <v>22</v>
+      </c>
+      <c r="F12" s="1">
         <v>-8490983.6853499375</v>
       </c>
     </row>
@@ -475,3241 +473,3238 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH32"/>
+  <dimension ref="A1:AG32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="K1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="M1" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="N1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="O1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="P1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="Q1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="R1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="T1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="U1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="V1" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="W1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="X1" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Y1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="Z1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="AA1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="AB1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AC1" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="AD1" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="AE1" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="AF1" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="AG1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="B2" s="1">
         <v>5.3208728745952945</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>3.7484951633997321</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>0.0074619786180935661</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>-0.00011549928927790545</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>0.0029402745072065958</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>0.0044296252455853502</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>0.0044914631641511521</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>0.003917003617875961</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>0.00011060729249211254</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0.0020647878163291295</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>-0.16002207442123756</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>-0.27382439405971465</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>-0.2952157743693597</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>0.10336501855755574</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>0.024960377845010026</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>0.010317834838711222</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="1">
         <v>0.0080292850139715155</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="1">
         <v>0.0083278885242810755</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="1">
         <v>0.00072946685942785333</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="1">
         <v>-0.001337400364782651</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="1">
         <v>0.0064461189337083709</v>
       </c>
-      <c r="W2">
+      <c r="W2" s="1">
         <v>-0.00054098192779851505</v>
       </c>
-      <c r="X2">
+      <c r="X2" s="1">
         <v>-0.0015090984426020075</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="1">
         <v>-0.0074801126726030277</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="1">
         <v>-0.000107225979501583</v>
       </c>
-      <c r="AA2">
+      <c r="AA2" s="1">
         <v>0.0050168093803972906</v>
       </c>
-      <c r="AB2">
+      <c r="AB2" s="1">
         <v>-0.00012045374260214435</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="1">
         <v>-0.006788450425532019</v>
       </c>
-      <c r="AD2">
+      <c r="AD2" s="1">
         <v>-0.0076893863307906894</v>
       </c>
-      <c r="AE2">
+      <c r="AE2" s="1">
         <v>-0.0083797414460541411</v>
       </c>
-      <c r="AF2">
+      <c r="AF2" s="1">
         <v>-0.0073977080619296327</v>
       </c>
-      <c r="AG2">
+      <c r="AG2" s="1">
         <v>-0.10376090035732416</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1">
         <v>0.25660804734378823</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>0.0074619786180935661</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>0.00091991975976539703</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>-1.4213243018956561e-05</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>-2.1193890415056871e-07</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>1.5963154301031068e-05</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>3.397727994038785e-06</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>1.7246800588431761e-05</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>-0.00011464519126682532</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>-3.3915049872848936e-05</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>-0.00031489868125120484</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>0.00026355745193258617</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>-0.00040766012155536019</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>-6.7868151593692902e-05</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>-0.00020602420798239429</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>-0.00033137009000187736</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>-0.00043268320592882836</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>-0.00040130700289875811</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>-0.00012346535882514246</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>-0.00010036826574645868</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="1">
         <v>0.0004859615196227407</v>
       </c>
-      <c r="W3">
+      <c r="W3" s="1">
         <v>-0.0001655808400051794</v>
       </c>
-      <c r="X3">
+      <c r="X3" s="1">
         <v>-6.5682366953170824e-06</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" s="1">
         <v>0.00056813600993383816</v>
       </c>
-      <c r="Z3">
+      <c r="Z3" s="1">
         <v>2.5675321573414341e-05</v>
       </c>
-      <c r="AA3">
+      <c r="AA3" s="1">
         <v>0.00025588722044885665</v>
       </c>
-      <c r="AB3">
+      <c r="AB3" s="1">
         <v>-7.8152998665457574e-06</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="1">
         <v>-6.1077605537123087e-05</v>
       </c>
-      <c r="AD3">
+      <c r="AD3" s="1">
         <v>-0.00013191929857380531</v>
       </c>
-      <c r="AE3">
+      <c r="AE3" s="1">
         <v>-0.00035349287150833941</v>
       </c>
-      <c r="AF3">
+      <c r="AF3" s="1">
         <v>-8.8866849927382162e-05</v>
       </c>
-      <c r="AG3">
+      <c r="AG3" s="1">
         <v>-0.015465113310734094</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4">
+        <v>27</v>
+      </c>
+      <c r="B4" s="1">
         <v>-0.0048277603411454716</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>-0.00011549928927790545</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>-1.4213243018956561e-05</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>2.2333897089541656e-07</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>6.1333013440666471e-07</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>7.8311861623724371e-07</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>1.191395224034214e-06</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>1.3448633221801082e-06</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>2.9544963740435384e-06</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>1.4690722318061507e-06</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>4.9171348871242503e-06</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>-4.975260866229577e-06</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>6.747925761945586e-06</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>1.026147134176533e-06</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>2.7528402898979693e-06</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>5.7281819702357209e-06</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>7.612123011174693e-06</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>6.9089453897036509e-06</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>1.4925737552708181e-06</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>2.5492696333441679e-06</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="1">
         <v>-7.444270351782648e-06</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="1">
         <v>2.5270247102234733e-06</v>
       </c>
-      <c r="X4">
+      <c r="X4" s="1">
         <v>1.0458098796920007e-07</v>
       </c>
-      <c r="Y4">
+      <c r="Y4" s="1">
         <v>-8.0920356600114696e-06</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" s="1">
         <v>-1.0629109360744537e-08</v>
       </c>
-      <c r="AA4">
+      <c r="AA4" s="1">
         <v>-4.1403087492336763e-06</v>
       </c>
-      <c r="AB4">
+      <c r="AB4" s="1">
         <v>1.260860106406014e-07</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="1">
         <v>7.9133955206712636e-07</v>
       </c>
-      <c r="AD4">
+      <c r="AD4" s="1">
         <v>1.7252290634346339e-06</v>
       </c>
-      <c r="AE4">
+      <c r="AE4" s="1">
         <v>5.6286347976563562e-06</v>
       </c>
-      <c r="AF4">
+      <c r="AF4" s="1">
         <v>1.2703278123123824e-06</v>
       </c>
-      <c r="AG4">
+      <c r="AG4" s="1">
         <v>0.00023431293734277461</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5">
+        <v>28</v>
+      </c>
+      <c r="B5" s="1">
         <v>-0.64786003402917569</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>0.0029402745072065958</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>-2.1193890415056871e-07</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>6.1333013440666471e-07</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.067244924916408252</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>0.048018439283880721</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>0.048150296987230237</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>0.04811328102689888</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>0.00058286276707386619</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0.00010378245230997871</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>-0.00010844658962529813</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>-0.00060599572910764038</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>-0.00049963225064508787</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>4.3425355727613746e-05</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>0.00051800823138674346</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>-0.0003411555211001345</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>1.5769145157492476e-05</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>0.00018274757248038648</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>-0.00015964898992758443</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>0.00020786468425862403</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="1">
         <v>0.00092408559158624467</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="1">
         <v>-1.8724400295022043e-05</v>
       </c>
-      <c r="X5">
+      <c r="X5" s="1">
         <v>1.9447919060433354e-05</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" s="1">
         <v>0.00021421414388690663</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="1">
         <v>0.00057247407834511502</v>
       </c>
-      <c r="AA5">
+      <c r="AA5" s="1">
         <v>0.00016780265931654048</v>
       </c>
-      <c r="AB5">
+      <c r="AB5" s="1">
         <v>-4.6062043033606227e-06</v>
       </c>
-      <c r="AC5">
+      <c r="AC5" s="1">
         <v>-0.00014998199023391742</v>
       </c>
-      <c r="AD5">
+      <c r="AD5" s="1">
         <v>-0.00022098436365655151</v>
       </c>
-      <c r="AE5">
+      <c r="AE5" s="1">
         <v>0.00025525825798129037</v>
       </c>
-      <c r="AF5">
+      <c r="AF5" s="1">
         <v>0.00021898721387131695</v>
       </c>
-      <c r="AG5">
+      <c r="AG5" s="1">
         <v>-0.051380044943535486</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6">
+        <v>29</v>
+      </c>
+      <c r="B6" s="1">
         <v>-0.37112149481184581</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>0.0044296252455853502</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>1.5963154301031068e-05</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>7.8311861623724371e-07</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>0.048018439283880721</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>0.051473997075715081</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>0.048845677424588105</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>0.048829392812922125</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>0.00098366086907256817</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>-0.00013469613099790449</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>-0.00015924205253731519</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>-0.00092527246477673575</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>-0.00078793415805674186</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>-6.7176037209175365e-05</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>0.00066745002918119217</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>-0.00081383456880185483</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>-0.00041229223526476066</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>-0.00051524089227576383</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <v>-0.00026606737744480462</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="1">
         <v>0.00036352103900037097</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="1">
         <v>0.0015809571667475767</v>
       </c>
-      <c r="W6">
+      <c r="W6" s="1">
         <v>5.9622472101828191e-05</v>
       </c>
-      <c r="X6">
+      <c r="X6" s="1">
         <v>2.6830307515770917e-05</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" s="1">
         <v>0.00026487519734304157</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="1">
         <v>0.00090150223924352971</v>
       </c>
-      <c r="AA6">
+      <c r="AA6" s="1">
         <v>0.00010717405966274678</v>
       </c>
-      <c r="AB6">
+      <c r="AB6" s="1">
         <v>-2.4747574565109017e-06</v>
       </c>
-      <c r="AC6">
+      <c r="AC6" s="1">
         <v>5.5310600811454228e-05</v>
       </c>
-      <c r="AD6">
+      <c r="AD6" s="1">
         <v>-8.424078095265429e-05</v>
       </c>
-      <c r="AE6">
+      <c r="AE6" s="1">
         <v>0.00029360963573863037</v>
       </c>
-      <c r="AF6">
+      <c r="AF6" s="1">
         <v>0.00013859467638739837</v>
       </c>
-      <c r="AG6">
+      <c r="AG6" s="1">
         <v>-0.052309751881999156</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7">
+        <v>30</v>
+      </c>
+      <c r="B7" s="1">
         <v>-0.22832885973410233</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>0.0044914631641511521</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>3.397727994038785e-06</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>1.191395224034214e-06</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>0.048150296987230237</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>0.048845677424588105</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>0.04951848952031597</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>0.049156455333415436</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>0.0009661885926587413</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>-9.0426622293397589e-05</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>-0.000149422347095092</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>-0.00083928788194015391</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>-0.0009656244418797047</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>-0.00046254573707026764</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>0.0011605700060992874</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>-0.00073356741192742887</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>-0.00040140998814373191</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>-0.00042737719293179863</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="1">
         <v>-0.0002905281242202018</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="1">
         <v>0.00017840774700668069</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="1">
         <v>0.0017045575087913897</v>
       </c>
-      <c r="W7">
+      <c r="W7" s="1">
         <v>-7.2236709194741674e-05</v>
       </c>
-      <c r="X7">
+      <c r="X7" s="1">
         <v>2.4861762427520577e-05</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="1">
         <v>-5.8633826320072472e-05</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="1">
         <v>0.00098492379203884636</v>
       </c>
-      <c r="AA7">
+      <c r="AA7" s="1">
         <v>-0.00012621001894942696</v>
       </c>
-      <c r="AB7">
+      <c r="AB7" s="1">
         <v>4.4434347457770009e-06</v>
       </c>
-      <c r="AC7">
+      <c r="AC7" s="1">
         <v>3.191585564930443e-05</v>
       </c>
-      <c r="AD7">
+      <c r="AD7" s="1">
         <v>0.00027192978722001722</v>
       </c>
-      <c r="AE7">
+      <c r="AE7" s="1">
         <v>0.00044906228715563788</v>
       </c>
-      <c r="AF7">
+      <c r="AF7" s="1">
         <v>0.00031826684568295248</v>
       </c>
-      <c r="AG7">
+      <c r="AG7" s="1">
         <v>-0.050744972872259708</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8">
+        <v>31</v>
+      </c>
+      <c r="B8" s="1">
         <v>-0.27893330952929823</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>0.003917003617875961</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>1.7246800588431761e-05</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>1.3448633221801082e-06</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>0.04811328102689888</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>0.048829392812922125</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>0.049156455333415436</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>0.050136412078277126</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>0.00098793973215630104</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>-5.3542220384470395e-05</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>-0.00016130673434672574</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>-0.00080003983452688054</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>-0.00099923007898035376</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>0.00086771088075274228</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>0.00060119085421536655</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>-0.00090659527031544066</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>-0.0006257565794932328</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>-0.00055870887324670909</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>-0.00027688767236442278</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="1">
         <v>0.00021346540656328947</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="1">
         <v>0.0018171667924808234</v>
       </c>
-      <c r="W8">
+      <c r="W8" s="1">
         <v>-6.4532393471618594e-05</v>
       </c>
-      <c r="X8">
+      <c r="X8" s="1">
         <v>3.5623179406455222e-06</v>
       </c>
-      <c r="Y8">
+      <c r="Y8" s="1">
         <v>0.0001005202995756258</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="1">
         <v>0.0010087907481478135</v>
       </c>
-      <c r="AA8">
+      <c r="AA8" s="1">
         <v>6.4518154382126394e-05</v>
       </c>
-      <c r="AB8">
+      <c r="AB8" s="1">
         <v>-1.370833681149067e-06</v>
       </c>
-      <c r="AC8">
+      <c r="AC8" s="1">
         <v>0.00012447072082982054</v>
       </c>
-      <c r="AD8">
+      <c r="AD8" s="1">
         <v>0.00033081140110419877</v>
       </c>
-      <c r="AE8">
+      <c r="AE8" s="1">
         <v>0.00038317126559262935</v>
       </c>
-      <c r="AF8">
+      <c r="AF8" s="1">
         <v>0.00045380117049193403</v>
       </c>
-      <c r="AG8">
+      <c r="AG8" s="1">
         <v>-0.051828397656293518</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9">
+        <v>32</v>
+      </c>
+      <c r="B9" s="1">
         <v>-1.5551200880815557</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>0.00011060729249211254</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>-0.00011464519126682532</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>2.9544963740435384e-06</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>0.00058286276707386619</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>0.00098366086907256817</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>0.0009661885926587413</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>0.00098793973215630104</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>0.0098991852813465307</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>-0.0075324565562944097</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>4.4903994116973637e-05</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>-0.0099026255333000846</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>0.00810492257288822</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>8.7700364953193118e-06</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>0.00051035411498770271</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>0.00049749903095692224</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>0.00076921129975771074</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>0.00070539135402109617</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <v>-0.00010964939803992672</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="1">
         <v>0.00027538605882888672</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="1">
         <v>-1.5816176540405313e-05</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="1">
         <v>-8.1658010875480417e-05</v>
       </c>
-      <c r="X9">
+      <c r="X9" s="1">
         <v>-5.3209396917830009e-06</v>
       </c>
-      <c r="Y9">
+      <c r="Y9" s="1">
         <v>-0.00063846039256207918</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="1">
         <v>0.00026991461659692034</v>
       </c>
-      <c r="AA9">
+      <c r="AA9" s="1">
         <v>-0.00019478791403503937</v>
       </c>
-      <c r="AB9">
+      <c r="AB9" s="1">
         <v>6.132356725991555e-06</v>
       </c>
-      <c r="AC9">
+      <c r="AC9" s="1">
         <v>-0.00017006714718149885</v>
       </c>
-      <c r="AD9">
+      <c r="AD9" s="1">
         <v>-3.6197568402529436e-05</v>
       </c>
-      <c r="AE9">
+      <c r="AE9" s="1">
         <v>0.00024423981823125515</v>
       </c>
-      <c r="AF9">
+      <c r="AF9" s="1">
         <v>-0.00017303076355890172</v>
       </c>
-      <c r="AG9">
+      <c r="AG9" s="1">
         <v>0.00067060987598661047</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1">
         <v>0.52299839524502967</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>0.0020647878163291295</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>-3.3915049872848936e-05</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>1.4690722318061507e-06</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>0.00010378245230997871</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>-0.00013469613099790449</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>-9.0426622293397589e-05</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>-5.3542220384470395e-05</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>-0.0075324565562944097</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.0090141502895321312</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>-6.3147901423640318e-05</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>0.0070036093477188928</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>-0.0078569623456789181</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>0.00037759730195765194</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>0.00014612277762118949</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>0.0011001088068455886</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>0.0013126761609678957</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>0.0016352338272550559</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="1">
         <v>0.00024098485107874014</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="1">
         <v>0.00032462167340586913</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="1">
         <v>-9.2013042427994997e-05</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="1">
         <v>-0.00015529414545660205</v>
       </c>
-      <c r="X10">
+      <c r="X10" s="1">
         <v>-2.2781702489131791e-05</v>
       </c>
-      <c r="Y10">
+      <c r="Y10" s="1">
         <v>0.00045747566471717848</v>
       </c>
-      <c r="Z10">
+      <c r="Z10" s="1">
         <v>0.00034020891134389287</v>
       </c>
-      <c r="AA10">
+      <c r="AA10" s="1">
         <v>9.3059784227006947e-05</v>
       </c>
-      <c r="AB10">
+      <c r="AB10" s="1">
         <v>-2.5367595678002187e-06</v>
       </c>
-      <c r="AC10">
+      <c r="AC10" s="1">
         <v>7.3053681462287811e-05</v>
       </c>
-      <c r="AD10">
+      <c r="AD10" s="1">
         <v>0.00010998602768836301</v>
       </c>
-      <c r="AE10">
+      <c r="AE10" s="1">
         <v>5.3932431972644312e-06</v>
       </c>
-      <c r="AF10">
+      <c r="AF10" s="1">
         <v>5.0959898316985303e-05</v>
       </c>
-      <c r="AG10">
+      <c r="AG10" s="1">
         <v>-0.0022862923980076057</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1">
         <v>-0.22575846207379349</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>-0.16002207442123756</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>-0.00031489868125120484</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>4.9171348871242503e-06</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>-0.00010844658962529813</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>-0.00015924205253731519</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>-0.000149422347095092</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>-0.00016130673434672574</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>4.4903994116973637e-05</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>-6.3147901423640318e-05</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>0.007056593349253678</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>0.012470402673272648</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>0.0087504418866377887</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>-0.0060365451996102666</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>-0.00095960816900608195</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>-0.00052329139877669293</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>-0.00042112384999733795</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>-0.00043111796066267654</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <v>-2.3260121720147732e-05</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="1">
         <v>6.1800786640875145e-05</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="1">
         <v>-0.00023709341804351518</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="1">
         <v>4.5757618385062838e-05</v>
       </c>
-      <c r="X11">
+      <c r="X11" s="1">
         <v>6.8204202039312485e-05</v>
       </c>
-      <c r="Y11">
+      <c r="Y11" s="1">
         <v>-0.0001259898329563524</v>
       </c>
-      <c r="Z11">
+      <c r="Z11" s="1">
         <v>-2.6936603895202048e-06</v>
       </c>
-      <c r="AA11">
+      <c r="AA11" s="1">
         <v>-0.00021885993258687926</v>
       </c>
-      <c r="AB11">
+      <c r="AB11" s="1">
         <v>5.2951149135251229e-06</v>
       </c>
-      <c r="AC11">
+      <c r="AC11" s="1">
         <v>0.00029114423321167243</v>
       </c>
-      <c r="AD11">
+      <c r="AD11" s="1">
         <v>0.00033638103677065652</v>
       </c>
-      <c r="AE11">
+      <c r="AE11" s="1">
         <v>0.00036754751359776747</v>
       </c>
-      <c r="AF11">
+      <c r="AF11" s="1">
         <v>0.00031564496351500375</v>
       </c>
-      <c r="AG11">
+      <c r="AG11" s="1">
         <v>0.0041993662185908776</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1">
         <v>-1.8090377565690556</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>-0.27382439405971465</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>0.00026355745193258617</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>-4.975260866229577e-06</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>-0.00060599572910764038</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>-0.00092527246477673575</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>-0.00083928788194015391</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>-0.00080003983452688054</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>-0.0099026255333000846</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0.0070036093477188928</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>0.012470402673272648</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>0.26597187240382947</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>-0.2153112072941018</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>-0.020381119177352223</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>-0.0042265307925190973</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="1">
         <v>-0.0046388739505642063</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="1">
         <v>-0.0048710201420698804</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <v>-0.0048705169932170243</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <v>-3.5967027350947926e-05</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="1">
         <v>-0.00015089127995918258</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="1">
         <v>-9.2607666645544692e-05</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="1">
         <v>7.3002202882016136e-05</v>
       </c>
-      <c r="X12">
+      <c r="X12" s="1">
         <v>0.00012861764120012574</v>
       </c>
-      <c r="Y12">
+      <c r="Y12" s="1">
         <v>-0.0001041281974325219</v>
       </c>
-      <c r="Z12">
+      <c r="Z12" s="1">
         <v>-0.00074459347889454641</v>
       </c>
-      <c r="AA12">
+      <c r="AA12" s="1">
         <v>-0.00045331155534306859</v>
       </c>
-      <c r="AB12">
+      <c r="AB12" s="1">
         <v>9.1825403934110711e-06</v>
       </c>
-      <c r="AC12">
+      <c r="AC12" s="1">
         <v>0.00061503705951100845</v>
       </c>
-      <c r="AD12">
+      <c r="AD12" s="1">
         <v>0.00075029447044723031</v>
       </c>
-      <c r="AE12">
+      <c r="AE12" s="1">
         <v>2.3064647196132781e-05</v>
       </c>
-      <c r="AF12">
+      <c r="AF12" s="1">
         <v>0.00096389054516403936</v>
       </c>
-      <c r="AG12">
+      <c r="AG12" s="1">
         <v>0.0010351810533156154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1">
         <v>0.36773934799947872</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>-0.2952157743693597</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>-0.00040766012155536019</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>6.747925761945586e-06</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>-0.00049963225064508787</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>-0.00078793415805674186</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>-0.0009656244418797047</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>-0.00099923007898035376</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>0.00810492257288822</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>-0.0078569623456789181</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>0.0087504418866377887</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>-0.2153112072941018</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>0.32713137020306493</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>0.0055384136467444773</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>-0.0013945719660508379</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>0.004129317273767431</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="1">
         <v>0.0045271692058439011</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <v>0.0040710847336898944</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <v>-0.00059661731612643462</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="1">
         <v>0.00026655340281516582</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="1">
         <v>-0.00032621811913825723</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="1">
         <v>0.00013751399824437867</v>
       </c>
-      <c r="X13">
+      <c r="X13" s="1">
         <v>0.00011820726773439711</v>
       </c>
-      <c r="Y13">
+      <c r="Y13" s="1">
         <v>0.00258671514044674</v>
       </c>
-      <c r="Z13">
+      <c r="Z13" s="1">
         <v>0.00092924850408484193</v>
       </c>
-      <c r="AA13">
+      <c r="AA13" s="1">
         <v>-0.0002392658759299725</v>
       </c>
-      <c r="AB13">
+      <c r="AB13" s="1">
         <v>5.7979470541125061e-06</v>
       </c>
-      <c r="AC13">
+      <c r="AC13" s="1">
         <v>2.3700567251091754e-05</v>
       </c>
-      <c r="AD13">
+      <c r="AD13" s="1">
         <v>0.00021726764560272185</v>
       </c>
-      <c r="AE13">
+      <c r="AE13" s="1">
         <v>0.00057857216971576083</v>
       </c>
-      <c r="AF13">
+      <c r="AF13" s="1">
         <v>-4.1682623424139581e-05</v>
       </c>
-      <c r="AG13">
+      <c r="AG13" s="1">
         <v>3.1580186061831977e-05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1">
         <v>0.56701355160433953</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>0.10336501855755574</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>-6.7868151593692902e-05</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>1.026147134176533e-06</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>4.3425355727613746e-05</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>-6.7176037209175365e-05</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>-0.00046254573707026764</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>0.00086771088075274228</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>8.7700364953193118e-06</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>0.00037759730195765194</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>-0.0060365451996102666</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>-0.020381119177352223</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>0.0055384136467444773</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>0.055632664714525798</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>-0.0037842108721536693</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="1">
         <v>-0.00066970644179095945</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="1">
         <v>-0.00068762734844855344</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <v>-0.00051691413754422822</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <v>0.00034624627124080345</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="1">
         <v>-0.00023036916449984828</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="1">
         <v>0.00015499420505785526</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="1">
         <v>0.00010627646729245599</v>
       </c>
-      <c r="X14">
+      <c r="X14" s="1">
         <v>-0.00019861518184589736</v>
       </c>
-      <c r="Y14">
+      <c r="Y14" s="1">
         <v>0.00049681082314396053</v>
       </c>
-      <c r="Z14">
+      <c r="Z14" s="1">
         <v>0.00016882501576015755</v>
       </c>
-      <c r="AA14">
+      <c r="AA14" s="1">
         <v>0.00016669845338956101</v>
       </c>
-      <c r="AB14">
+      <c r="AB14" s="1">
         <v>-4.1357331342271998e-06</v>
       </c>
-      <c r="AC14">
+      <c r="AC14" s="1">
         <v>-0.00033976128242095782</v>
       </c>
-      <c r="AD14">
+      <c r="AD14" s="1">
         <v>0.0001621346262985713</v>
       </c>
-      <c r="AE14">
+      <c r="AE14" s="1">
         <v>-0.00045972533415868756</v>
       </c>
-      <c r="AF14">
+      <c r="AF14" s="1">
         <v>-0.000425978828580658</v>
       </c>
-      <c r="AG14">
+      <c r="AG14" s="1">
         <v>0.0091925838685297887</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15">
+        <v>38</v>
+      </c>
+      <c r="B15" s="1">
         <v>-0.076420266427702124</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>0.024960377845010026</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>-0.00020602420798239429</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>2.7528402898979693e-06</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>0.00051800823138674346</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>0.00066745002918119217</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>0.0011605700060992874</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>0.00060119085421536655</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>0.00051035411498770271</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>0.00014612277762118949</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>-0.00095960816900608195</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>-0.0042265307925190973</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>-0.0013945719660508379</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>-0.0037842108721536693</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>0.015933686188452135</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>0.0055869564563278381</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="1">
         <v>0.0056826516487664975</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <v>0.0058379885510559826</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <v>-8.5493601589560356e-05</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="1">
         <v>-3.0955376297289163e-05</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="1">
         <v>-0.0017514939672958025</v>
       </c>
-      <c r="W15">
+      <c r="W15" s="1">
         <v>-0.00028690110077254037</v>
       </c>
-      <c r="X15">
+      <c r="X15" s="1">
         <v>9.7831975890021346e-05</v>
       </c>
-      <c r="Y15">
+      <c r="Y15" s="1">
         <v>-0.00087096022308262024</v>
       </c>
-      <c r="Z15">
+      <c r="Z15" s="1">
         <v>0.00035508262006155706</v>
       </c>
-      <c r="AA15">
+      <c r="AA15" s="1">
         <v>-0.00081467862711195719</v>
       </c>
-      <c r="AB15">
+      <c r="AB15" s="1">
         <v>2.6746443939239778e-05</v>
       </c>
-      <c r="AC15">
+      <c r="AC15" s="1">
         <v>0.00041666002278044519</v>
       </c>
-      <c r="AD15">
+      <c r="AD15" s="1">
         <v>-0.00034213009193165094</v>
       </c>
-      <c r="AE15">
+      <c r="AE15" s="1">
         <v>0.0012066624855472099</v>
       </c>
-      <c r="AF15">
+      <c r="AF15" s="1">
         <v>0.00014999868022961041</v>
       </c>
-      <c r="AG15">
+      <c r="AG15" s="1">
         <v>-0.0017516908652561412</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16">
+        <v>39</v>
+      </c>
+      <c r="B16" s="1">
         <v>0.069876409395878941</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>0.010317834838711222</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>-0.00033137009000187736</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>5.7281819702357209e-06</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>-0.0003411555211001345</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>-0.00081383456880185483</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>-0.00073356741192742887</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>-0.00090659527031544066</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>0.00049749903095692224</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>0.0011001088068455886</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>-0.00052329139877669293</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>-0.0046388739505642063</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>0.004129317273767431</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="1">
         <v>-0.00066970644179095945</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="1">
         <v>0.0055869564563278381</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="1">
         <v>0.0087527343015599886</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="1">
         <v>0.0082732390537682207</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <v>0.0083767523558578461</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>-0.00029972799477533812</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>5.3449235099431794e-05</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="1">
         <v>-0.00096285542270438168</v>
       </c>
-      <c r="W16">
+      <c r="W16" s="1">
         <v>4.1158597895620832e-05</v>
       </c>
-      <c r="X16">
+      <c r="X16" s="1">
         <v>-1.694703934560708e-07</v>
       </c>
-      <c r="Y16">
+      <c r="Y16" s="1">
         <v>0.0027626113767705352</v>
       </c>
-      <c r="Z16">
+      <c r="Z16" s="1">
         <v>0.0011467779013342562</v>
       </c>
-      <c r="AA16">
+      <c r="AA16" s="1">
         <v>-9.4491802873651392e-05</v>
       </c>
-      <c r="AB16">
+      <c r="AB16" s="1">
         <v>3.2484938314088913e-06</v>
       </c>
-      <c r="AC16">
+      <c r="AC16" s="1">
         <v>8.7446169102046523e-05</v>
       </c>
-      <c r="AD16">
+      <c r="AD16" s="1">
         <v>-0.00023473282254862847</v>
       </c>
-      <c r="AE16">
+      <c r="AE16" s="1">
         <v>3.0478812118126452e-05</v>
       </c>
-      <c r="AF16">
+      <c r="AF16" s="1">
         <v>-0.00012879468234123262</v>
       </c>
-      <c r="AG16">
+      <c r="AG16" s="1">
         <v>-0.002363346887545241</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17">
+        <v>40</v>
+      </c>
+      <c r="B17" s="1">
         <v>0.020412997324607003</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>0.0080292850139715155</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>-0.00043268320592882836</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>7.612123011174693e-06</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>1.5769145157492476e-05</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>-0.00041229223526476066</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>-0.00040140998814373191</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>-0.0006257565794932328</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>0.00076921129975771074</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>0.0013126761609678957</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>-0.00042112384999733795</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>-0.0048710201420698804</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>0.0045271692058439011</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>-0.00068762734844855344</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>0.0056826516487664975</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>0.0082732390537682207</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>0.0096921408611985449</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <v>0.0091216053620932457</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>-0.00028312307376927512</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>0.00017463383965579953</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="1">
         <v>-0.00093538994883468249</v>
       </c>
-      <c r="W17">
+      <c r="W17" s="1">
         <v>-0.00011430813864056748</v>
       </c>
-      <c r="X17">
+      <c r="X17" s="1">
         <v>1.3080835351661545e-05</v>
       </c>
-      <c r="Y17">
+      <c r="Y17" s="1">
         <v>0.0031020345754607668</v>
       </c>
-      <c r="Z17">
+      <c r="Z17" s="1">
         <v>0.00172663220171237</v>
       </c>
-      <c r="AA17">
+      <c r="AA17" s="1">
         <v>-0.00011498656405461191</v>
       </c>
-      <c r="AB17">
+      <c r="AB17" s="1">
         <v>4.2775836643764735e-06</v>
       </c>
-      <c r="AC17">
+      <c r="AC17" s="1">
         <v>1.8200675238164789e-05</v>
       </c>
-      <c r="AD17">
+      <c r="AD17" s="1">
         <v>-0.00018914576186804136</v>
       </c>
-      <c r="AE17">
+      <c r="AE17" s="1">
         <v>8.0643513947799284e-05</v>
       </c>
-      <c r="AF17">
+      <c r="AF17" s="1">
         <v>-0.00010654230168147377</v>
       </c>
-      <c r="AG17">
+      <c r="AG17" s="1">
         <v>-0.0027763280727496724</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18">
+        <v>41</v>
+      </c>
+      <c r="B18" s="1">
         <v>0.022408314940740949</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>0.0083278885242810755</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>-0.00040130700289875811</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>6.9089453897036509e-06</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>0.00018274757248038648</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>-0.00051524089227576383</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>-0.00042737719293179863</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>-0.00055870887324670909</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>0.00070539135402109617</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>0.0016352338272550559</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>-0.00043111796066267654</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>-0.0048705169932170243</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>0.0040710847336898944</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>-0.00051691413754422822</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>0.0058379885510559826</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="1">
         <v>0.0083767523558578461</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="1">
         <v>0.0091216053620932457</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <v>0.010150979206107196</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <v>-0.00014287115093077301</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="1">
         <v>0.00021588445636633031</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="1">
         <v>-0.00086346361333901767</v>
       </c>
-      <c r="W18">
+      <c r="W18" s="1">
         <v>-0.00036350709014085257</v>
       </c>
-      <c r="X18">
+      <c r="X18" s="1">
         <v>7.3457852888917123e-06</v>
       </c>
-      <c r="Y18">
+      <c r="Y18" s="1">
         <v>0.0031954998205767421</v>
       </c>
-      <c r="Z18">
+      <c r="Z18" s="1">
         <v>0.0018580522888390647</v>
       </c>
-      <c r="AA18">
+      <c r="AA18" s="1">
         <v>-3.0950068808316866e-05</v>
       </c>
-      <c r="AB18">
+      <c r="AB18" s="1">
         <v>1.3371184384409675e-06</v>
       </c>
-      <c r="AC18">
+      <c r="AC18" s="1">
         <v>5.1694037399498642e-05</v>
       </c>
-      <c r="AD18">
+      <c r="AD18" s="1">
         <v>-0.00011969739202040137</v>
       </c>
-      <c r="AE18">
+      <c r="AE18" s="1">
         <v>0.00018706677962094013</v>
       </c>
-      <c r="AF18">
+      <c r="AF18" s="1">
         <v>3.011872967537512e-05</v>
       </c>
-      <c r="AG18">
+      <c r="AG18" s="1">
         <v>-0.0037696055064498375</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19">
+        <v>42</v>
+      </c>
+      <c r="B19" s="1">
         <v>-0.21644974549152668</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>0.00072946685942785333</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>-0.00012346535882514246</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>1.4925737552708181e-06</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>-0.00015964898992758443</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>-0.00026606737744480462</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>-0.0002905281242202018</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>-0.00027688767236442278</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>-0.00010964939803992672</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>0.00024098485107874014</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>-2.3260121720147732e-05</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>-3.5967027350947926e-05</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>-0.00059661731612643462</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>0.00034624627124080345</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>-8.5493601589560356e-05</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>-0.00029972799477533812</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="1">
         <v>-0.00028312307376927512</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <v>-0.00014287115093077301</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <v>0.00049324436474827292</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="1">
         <v>-0.0003235363270097155</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="1">
         <v>-2.4054516382655183e-05</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="1">
         <v>6.729837599283236e-05</v>
       </c>
-      <c r="X19">
+      <c r="X19" s="1">
         <v>-5.4254457073987599e-06</v>
       </c>
-      <c r="Y19">
+      <c r="Y19" s="1">
         <v>-0.00017683980036423136</v>
       </c>
-      <c r="Z19">
+      <c r="Z19" s="1">
         <v>-0.00010497449260103941</v>
       </c>
-      <c r="AA19">
+      <c r="AA19" s="1">
         <v>4.0685724104127917e-05</v>
       </c>
-      <c r="AB19">
+      <c r="AB19" s="1">
         <v>-1.1167779409844421e-06</v>
       </c>
-      <c r="AC19">
+      <c r="AC19" s="1">
         <v>1.0196747951565465e-05</v>
       </c>
-      <c r="AD19">
+      <c r="AD19" s="1">
         <v>0.00012872200597995842</v>
       </c>
-      <c r="AE19">
+      <c r="AE19" s="1">
         <v>-1.4078523221663908e-05</v>
       </c>
-      <c r="AF19">
+      <c r="AF19" s="1">
         <v>2.8228823980311792e-05</v>
       </c>
-      <c r="AG19">
+      <c r="AG19" s="1">
         <v>0.0023197227136744353</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20">
+        <v>43</v>
+      </c>
+      <c r="B20" s="1">
         <v>-0.020311741055469575</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>-0.001337400364782651</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>-0.00010036826574645868</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>2.5492696333441679e-06</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>0.00020786468425862403</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>0.00036352103900037097</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>0.00017840774700668069</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>0.00021346540656328947</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>0.00027538605882888672</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>0.00032462167340586913</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>6.1800786640875145e-05</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>-0.00015089127995918258</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>0.00026655340281516582</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>-0.00023036916449984828</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>-3.0955376297289163e-05</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>5.3449235099431794e-05</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="1">
         <v>0.00017463383965579953</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="1">
         <v>0.00021588445636633031</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <v>-0.0003235363270097155</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="1">
         <v>0.0016833105852748541</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="1">
         <v>-6.355599153641913e-05</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="1">
         <v>-0.00020679976412711333</v>
       </c>
-      <c r="X20">
+      <c r="X20" s="1">
         <v>1.7874666903332239e-06</v>
       </c>
-      <c r="Y20">
+      <c r="Y20" s="1">
         <v>0.00012597046080325267</v>
       </c>
-      <c r="Z20">
+      <c r="Z20" s="1">
         <v>-0.00021628523712120367</v>
       </c>
-      <c r="AA20">
+      <c r="AA20" s="1">
         <v>3.3417611932781189e-05</v>
       </c>
-      <c r="AB20">
+      <c r="AB20" s="1">
         <v>-8.157872173171664e-07</v>
       </c>
-      <c r="AC20">
+      <c r="AC20" s="1">
         <v>-1.030351860063561e-05</v>
       </c>
-      <c r="AD20">
+      <c r="AD20" s="1">
         <v>-0.00016317819745507284</v>
       </c>
-      <c r="AE20">
+      <c r="AE20" s="1">
         <v>0.00016773872132149051</v>
       </c>
-      <c r="AF20">
+      <c r="AF20" s="1">
         <v>-3.2514776949134919e-05</v>
       </c>
-      <c r="AG20">
+      <c r="AG20" s="1">
         <v>-0.00023464117456450375</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21">
+        <v>44</v>
+      </c>
+      <c r="B21" s="1">
         <v>0.15445805652328945</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>0.0064461189337083709</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>0.0004859615196227407</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>-7.444270351782648e-06</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>0.00092408559158624467</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>0.0015809571667475767</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>0.0017045575087913897</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>0.0018171667924808234</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <v>-1.5816176540405313e-05</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>-9.2013042427994997e-05</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>-0.00023709341804351518</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <v>-9.2607666645544692e-05</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <v>-0.00032621811913825723</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="1">
         <v>0.00015499420505785526</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="1">
         <v>-0.0017514939672958025</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="1">
         <v>-0.00096285542270438168</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="1">
         <v>-0.00093538994883468249</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="1">
         <v>-0.00086346361333901767</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="1">
         <v>-2.4054516382655183e-05</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="1">
         <v>-6.355599153641913e-05</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="1">
         <v>0.0053730864593817861</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="1">
         <v>0.00039506248232392197</v>
       </c>
-      <c r="X21">
+      <c r="X21" s="1">
         <v>-1.0220372318966314e-05</v>
       </c>
-      <c r="Y21">
+      <c r="Y21" s="1">
         <v>-7.0860039454783281e-05</v>
       </c>
-      <c r="Z21">
+      <c r="Z21" s="1">
         <v>-0.00013817345709455427</v>
       </c>
-      <c r="AA21">
+      <c r="AA21" s="1">
         <v>0.00039649476336338086</v>
       </c>
-      <c r="AB21">
+      <c r="AB21" s="1">
         <v>-1.2292755899290081e-05</v>
       </c>
-      <c r="AC21">
+      <c r="AC21" s="1">
         <v>-0.00012351588704774389</v>
       </c>
-      <c r="AD21">
+      <c r="AD21" s="1">
         <v>0.00022616507678797806</v>
       </c>
-      <c r="AE21">
+      <c r="AE21" s="1">
         <v>-0.00046969471098306733</v>
       </c>
-      <c r="AF21">
+      <c r="AF21" s="1">
         <v>-9.070496986821622e-05</v>
       </c>
-      <c r="AG21">
+      <c r="AG21" s="1">
         <v>-0.011344599918700774</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22">
+        <v>45</v>
+      </c>
+      <c r="B22" s="1">
         <v>0.081805595316038565</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>-0.00054098192779851505</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>-0.0001655808400051794</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>2.5270247102234733e-06</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>-1.8724400295022043e-05</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>5.9622472101828191e-05</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>-7.2236709194741674e-05</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="1">
         <v>-6.4532393471618594e-05</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="1">
         <v>-8.1658010875480417e-05</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>-0.00015529414545660205</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="1">
         <v>4.5757618385062838e-05</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="1">
         <v>7.3002202882016136e-05</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="1">
         <v>0.00013751399824437867</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="1">
         <v>0.00010627646729245599</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="1">
         <v>-0.00028690110077254037</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="1">
         <v>4.1158597895620832e-05</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="1">
         <v>-0.00011430813864056748</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="1">
         <v>-0.00036350709014085257</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="1">
         <v>6.729837599283236e-05</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="1">
         <v>-0.00020679976412711333</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="1">
         <v>0.00039506248232392197</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="1">
         <v>0.0012100028745859086</v>
       </c>
-      <c r="X22">
+      <c r="X22" s="1">
         <v>-9.8785929677321018e-06</v>
       </c>
-      <c r="Y22">
+      <c r="Y22" s="1">
         <v>-0.00019847813727260131</v>
       </c>
-      <c r="Z22">
+      <c r="Z22" s="1">
         <v>0.00015069438405955769</v>
       </c>
-      <c r="AA22">
+      <c r="AA22" s="1">
         <v>5.3613303448047929e-05</v>
       </c>
-      <c r="AB22">
+      <c r="AB22" s="1">
         <v>-2.0653315068987884e-06</v>
       </c>
-      <c r="AC22">
+      <c r="AC22" s="1">
         <v>7.7635174325486661e-05</v>
       </c>
-      <c r="AD22">
+      <c r="AD22" s="1">
         <v>1.1019690382003326e-05</v>
       </c>
-      <c r="AE22">
+      <c r="AE22" s="1">
         <v>-9.1587472475258965e-06</v>
       </c>
-      <c r="AF22">
+      <c r="AF22" s="1">
         <v>-3.1305119181720739e-05</v>
       </c>
-      <c r="AG22">
+      <c r="AG22" s="1">
         <v>0.0024175160597806871</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23">
+        <v>46</v>
+      </c>
+      <c r="B23" s="1">
         <v>0.01500883217575264</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="1">
         <v>-0.0015090984426020075</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="1">
         <v>-6.5682366953170824e-06</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>1.0458098796920007e-07</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <v>1.9447919060433354e-05</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>2.6830307515770917e-05</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>2.4861762427520577e-05</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="1">
         <v>3.5623179406455222e-06</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="1">
         <v>-5.3209396917830009e-06</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>-2.2781702489131791e-05</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="1">
         <v>6.8204202039312485e-05</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="1">
         <v>0.00012861764120012574</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="1">
         <v>0.00011820726773439711</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="1">
         <v>-0.00019861518184589736</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="1">
         <v>9.7831975890021346e-05</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="1">
         <v>-1.694703934560708e-07</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="1">
         <v>1.3080835351661545e-05</v>
       </c>
-      <c r="S23">
+      <c r="S23" s="1">
         <v>7.3457852888917123e-06</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="1">
         <v>-5.4254457073987599e-06</v>
       </c>
-      <c r="U23">
+      <c r="U23" s="1">
         <v>1.7874666903332239e-06</v>
       </c>
-      <c r="V23">
+      <c r="V23" s="1">
         <v>-1.0220372318966314e-05</v>
       </c>
-      <c r="W23">
+      <c r="W23" s="1">
         <v>-9.8785929677321018e-06</v>
       </c>
-      <c r="X23">
+      <c r="X23" s="1">
         <v>8.8139392008646699e-05</v>
       </c>
-      <c r="Y23">
+      <c r="Y23" s="1">
         <v>4.9525709655314626e-06</v>
       </c>
-      <c r="Z23">
+      <c r="Z23" s="1">
         <v>4.8036424395582044e-06</v>
       </c>
-      <c r="AA23">
+      <c r="AA23" s="1">
         <v>-0.00024256963935901711</v>
       </c>
-      <c r="AB23">
+      <c r="AB23" s="1">
         <v>6.7108969177095097e-06</v>
       </c>
-      <c r="AC23">
+      <c r="AC23" s="1">
         <v>-3.0994950307832841e-06</v>
       </c>
-      <c r="AD23">
+      <c r="AD23" s="1">
         <v>3.6771533621403145e-06</v>
       </c>
-      <c r="AE23">
+      <c r="AE23" s="1">
         <v>4.6824994534044905e-05</v>
       </c>
-      <c r="AF23">
+      <c r="AF23" s="1">
         <v>1.6404632511981916e-05</v>
       </c>
-      <c r="AG23">
+      <c r="AG23" s="1">
         <v>-0.0018532857615941927</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24">
+        <v>47</v>
+      </c>
+      <c r="B24" s="1">
         <v>-0.092281767204888968</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="1">
         <v>-0.0074801126726030277</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>0.00056813600993383816</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>-8.0920356600114696e-06</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <v>0.00021421414388690663</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <v>0.00026487519734304157</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>-5.8633826320072472e-05</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="1">
         <v>0.0001005202995756258</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="1">
         <v>-0.00063846039256207918</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="1">
         <v>0.00045747566471717848</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="1">
         <v>-0.0001259898329563524</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="1">
         <v>-0.0001041281974325219</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="1">
         <v>0.00258671514044674</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="1">
         <v>0.00049681082314396053</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="1">
         <v>-0.00087096022308262024</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="1">
         <v>0.0027626113767705352</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="1">
         <v>0.0031020345754607668</v>
       </c>
-      <c r="S24">
+      <c r="S24" s="1">
         <v>0.0031954998205767421</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="1">
         <v>-0.00017683980036423136</v>
       </c>
-      <c r="U24">
+      <c r="U24" s="1">
         <v>0.00012597046080325267</v>
       </c>
-      <c r="V24">
+      <c r="V24" s="1">
         <v>-7.0860039454783281e-05</v>
       </c>
-      <c r="W24">
+      <c r="W24" s="1">
         <v>-0.00019847813727260131</v>
       </c>
-      <c r="X24">
+      <c r="X24" s="1">
         <v>4.9525709655314626e-06</v>
       </c>
-      <c r="Y24">
+      <c r="Y24" s="1">
         <v>0.011366383616146477</v>
       </c>
-      <c r="Z24">
+      <c r="Z24" s="1">
         <v>0.0010243793563598103</v>
       </c>
-      <c r="AA24">
+      <c r="AA24" s="1">
         <v>0.00040960501123969034</v>
       </c>
-      <c r="AB24">
+      <c r="AB24" s="1">
         <v>-1.2990795551599569e-05</v>
       </c>
-      <c r="AC24">
+      <c r="AC24" s="1">
         <v>7.566914270684471e-05</v>
       </c>
-      <c r="AD24">
+      <c r="AD24" s="1">
         <v>-0.00029123616327819376</v>
       </c>
-      <c r="AE24">
+      <c r="AE24" s="1">
         <v>-0.00063571416678490783</v>
       </c>
-      <c r="AF24">
+      <c r="AF24" s="1">
         <v>1.2372478597373046e-05</v>
       </c>
-      <c r="AG24">
+      <c r="AG24" s="1">
         <v>-0.01599702719363004</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25">
+        <v>48</v>
+      </c>
+      <c r="B25" s="1">
         <v>-0.0038154611534171011</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="1">
         <v>-0.000107225979501583</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
         <v>2.5675321573414341e-05</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="1">
         <v>-1.0629109360744537e-08</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <v>0.00057247407834511502</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>0.00090150223924352971</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>0.00098492379203884636</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="1">
         <v>0.0010087907481478135</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="1">
         <v>0.00026991461659692034</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="1">
         <v>0.00034020891134389287</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="1">
         <v>-2.6936603895202048e-06</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="1">
         <v>-0.00074459347889454641</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="1">
         <v>0.00092924850408484193</v>
       </c>
-      <c r="O25">
+      <c r="O25" s="1">
         <v>0.00016882501576015755</v>
       </c>
-      <c r="P25">
+      <c r="P25" s="1">
         <v>0.00035508262006155706</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="1">
         <v>0.0011467779013342562</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="1">
         <v>0.00172663220171237</v>
       </c>
-      <c r="S25">
+      <c r="S25" s="1">
         <v>0.0018580522888390647</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="1">
         <v>-0.00010497449260103941</v>
       </c>
-      <c r="U25">
+      <c r="U25" s="1">
         <v>-0.00021628523712120367</v>
       </c>
-      <c r="V25">
+      <c r="V25" s="1">
         <v>-0.00013817345709455427</v>
       </c>
-      <c r="W25">
+      <c r="W25" s="1">
         <v>0.00015069438405955769</v>
       </c>
-      <c r="X25">
+      <c r="X25" s="1">
         <v>4.8036424395582044e-06</v>
       </c>
-      <c r="Y25">
+      <c r="Y25" s="1">
         <v>0.0010243793563598103</v>
       </c>
-      <c r="Z25">
+      <c r="Z25" s="1">
         <v>0.0020042836598365152</v>
       </c>
-      <c r="AA25">
+      <c r="AA25" s="1">
         <v>-0.00014300485896399728</v>
       </c>
-      <c r="AB25">
+      <c r="AB25" s="1">
         <v>4.5799706448885427e-06</v>
       </c>
-      <c r="AC25">
+      <c r="AC25" s="1">
         <v>-9.503994986286799e-05</v>
       </c>
-      <c r="AD25">
+      <c r="AD25" s="1">
         <v>0.0002345479464767585</v>
       </c>
-      <c r="AE25">
+      <c r="AE25" s="1">
         <v>3.3703277798702064e-05</v>
       </c>
-      <c r="AF25">
+      <c r="AF25" s="1">
         <v>-1.457645665327115e-05</v>
       </c>
-      <c r="AG25">
+      <c r="AG25" s="1">
         <v>-0.0030273463646026495</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26">
+        <v>49</v>
+      </c>
+      <c r="B26" s="1">
         <v>0.054066134085123188</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>0.0050168093803972906</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="1">
         <v>0.00025588722044885665</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>-4.1403087492336763e-06</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <v>0.00016780265931654048</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <v>0.00010717405966274678</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>-0.00012621001894942696</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="1">
         <v>6.4518154382126394e-05</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="1">
         <v>-0.00019478791403503937</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="1">
         <v>9.3059784227006947e-05</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="1">
         <v>-0.00021885993258687926</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="1">
         <v>-0.00045331155534306859</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="1">
         <v>-0.0002392658759299725</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="1">
         <v>0.00016669845338956101</v>
       </c>
-      <c r="P26">
+      <c r="P26" s="1">
         <v>-0.00081467862711195719</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="1">
         <v>-9.4491802873651392e-05</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="1">
         <v>-0.00011498656405461191</v>
       </c>
-      <c r="S26">
+      <c r="S26" s="1">
         <v>-3.0950068808316866e-05</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="1">
         <v>4.0685724104127917e-05</v>
       </c>
-      <c r="U26">
+      <c r="U26" s="1">
         <v>3.3417611932781189e-05</v>
       </c>
-      <c r="V26">
+      <c r="V26" s="1">
         <v>0.00039649476336338086</v>
       </c>
-      <c r="W26">
+      <c r="W26" s="1">
         <v>5.3613303448047929e-05</v>
       </c>
-      <c r="X26">
+      <c r="X26" s="1">
         <v>-0.00024256963935901711</v>
       </c>
-      <c r="Y26">
+      <c r="Y26" s="1">
         <v>0.00040960501123969034</v>
       </c>
-      <c r="Z26">
+      <c r="Z26" s="1">
         <v>-0.00014300485896399728</v>
       </c>
-      <c r="AA26">
+      <c r="AA26" s="1">
         <v>0.0025255565023293942</v>
       </c>
-      <c r="AB26">
+      <c r="AB26" s="1">
         <v>-7.3980063410541432e-05</v>
       </c>
-      <c r="AC26">
+      <c r="AC26" s="1">
         <v>-0.00018875670174356161</v>
       </c>
-      <c r="AD26">
+      <c r="AD26" s="1">
         <v>-7.7534695720057932e-05</v>
       </c>
-      <c r="AE26">
+      <c r="AE26" s="1">
         <v>-0.00051872767693485504</v>
       </c>
-      <c r="AF26">
+      <c r="AF26" s="1">
         <v>-0.0001079307930026867</v>
       </c>
-      <c r="AG26">
+      <c r="AG26" s="1">
         <v>-0.013075581650972921</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27">
+        <v>50</v>
+      </c>
+      <c r="B27" s="1">
         <v>-0.0021633520995904178</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>-0.00012045374260214435</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>-7.8152998665457574e-06</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1">
         <v>1.260860106406014e-07</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="1">
         <v>-4.6062043033606227e-06</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>-2.4747574565109017e-06</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>4.4434347457770009e-06</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="1">
         <v>-1.370833681149067e-06</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="1">
         <v>6.132356725991555e-06</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="1">
         <v>-2.5367595678002187e-06</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="1">
         <v>5.2951149135251229e-06</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="1">
         <v>9.1825403934110711e-06</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="1">
         <v>5.7979470541125061e-06</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="1">
         <v>-4.1357331342271998e-06</v>
       </c>
-      <c r="P27">
+      <c r="P27" s="1">
         <v>2.6746443939239778e-05</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="1">
         <v>3.2484938314088913e-06</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="1">
         <v>4.2775836643764735e-06</v>
       </c>
-      <c r="S27">
+      <c r="S27" s="1">
         <v>1.3371184384409675e-06</v>
       </c>
-      <c r="T27">
+      <c r="T27" s="1">
         <v>-1.1167779409844421e-06</v>
       </c>
-      <c r="U27">
+      <c r="U27" s="1">
         <v>-8.157872173171664e-07</v>
       </c>
-      <c r="V27">
+      <c r="V27" s="1">
         <v>-1.2292755899290081e-05</v>
       </c>
-      <c r="W27">
+      <c r="W27" s="1">
         <v>-2.0653315068987884e-06</v>
       </c>
-      <c r="X27">
+      <c r="X27" s="1">
         <v>6.7108969177095097e-06</v>
       </c>
-      <c r="Y27">
+      <c r="Y27" s="1">
         <v>-1.2990795551599569e-05</v>
       </c>
-      <c r="Z27">
+      <c r="Z27" s="1">
         <v>4.5799706448885427e-06</v>
       </c>
-      <c r="AA27">
+      <c r="AA27" s="1">
         <v>-7.3980063410541432e-05</v>
       </c>
-      <c r="AB27">
+      <c r="AB27" s="1">
         <v>2.1866403501647216e-06</v>
       </c>
-      <c r="AC27">
+      <c r="AC27" s="1">
         <v>5.9387872067744568e-06</v>
       </c>
-      <c r="AD27">
+      <c r="AD27" s="1">
         <v>2.5075647193059804e-06</v>
       </c>
-      <c r="AE27">
+      <c r="AE27" s="1">
         <v>1.6040497968779973e-05</v>
       </c>
-      <c r="AF27">
+      <c r="AF27" s="1">
         <v>3.1776309221621492e-06</v>
       </c>
-      <c r="AG27">
+      <c r="AG27" s="1">
         <v>0.00039927625109577281</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28">
+        <v>51</v>
+      </c>
+      <c r="B28" s="1">
         <v>0.012844387817267272</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>-0.006788450425532019</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="1">
         <v>-6.1077605537123087e-05</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="1">
         <v>7.9133955206712636e-07</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="1">
         <v>-0.00014998199023391742</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>5.5310600811454228e-05</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>3.191585564930443e-05</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="1">
         <v>0.00012447072082982054</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="1">
         <v>-0.00017006714718149885</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="1">
         <v>7.3053681462287811e-05</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="1">
         <v>0.00029114423321167243</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="1">
         <v>0.00061503705951100845</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="1">
         <v>2.3700567251091754e-05</v>
       </c>
-      <c r="O28">
+      <c r="O28" s="1">
         <v>-0.00033976128242095782</v>
       </c>
-      <c r="P28">
+      <c r="P28" s="1">
         <v>0.00041666002278044519</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" s="1">
         <v>8.7446169102046523e-05</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="1">
         <v>1.8200675238164789e-05</v>
       </c>
-      <c r="S28">
+      <c r="S28" s="1">
         <v>5.1694037399498642e-05</v>
       </c>
-      <c r="T28">
+      <c r="T28" s="1">
         <v>1.0196747951565465e-05</v>
       </c>
-      <c r="U28">
+      <c r="U28" s="1">
         <v>-1.030351860063561e-05</v>
       </c>
-      <c r="V28">
+      <c r="V28" s="1">
         <v>-0.00012351588704774389</v>
       </c>
-      <c r="W28">
+      <c r="W28" s="1">
         <v>7.7635174325486661e-05</v>
       </c>
-      <c r="X28">
+      <c r="X28" s="1">
         <v>-3.0994950307832841e-06</v>
       </c>
-      <c r="Y28">
+      <c r="Y28" s="1">
         <v>7.566914270684471e-05</v>
       </c>
-      <c r="Z28">
+      <c r="Z28" s="1">
         <v>-9.503994986286799e-05</v>
       </c>
-      <c r="AA28">
+      <c r="AA28" s="1">
         <v>-0.00018875670174356161</v>
       </c>
-      <c r="AB28">
+      <c r="AB28" s="1">
         <v>5.9387872067744568e-06</v>
       </c>
-      <c r="AC28">
+      <c r="AC28" s="1">
         <v>0.0028085411300240522</v>
       </c>
-      <c r="AD28">
+      <c r="AD28" s="1">
         <v>0.001250501091349832</v>
       </c>
-      <c r="AE28">
+      <c r="AE28" s="1">
         <v>0.0012776085422094516</v>
       </c>
-      <c r="AF28">
+      <c r="AF28" s="1">
         <v>0.0012391383066635581</v>
       </c>
-      <c r="AG28">
+      <c r="AG28" s="1">
         <v>0.0013246249422361656</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29">
+        <v>52</v>
+      </c>
+      <c r="B29" s="1">
         <v>0.060670794220606165</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>-0.0076893863307906894</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="1">
         <v>-0.00013191929857380531</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="1">
         <v>1.7252290634346339e-06</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="1">
         <v>-0.00022098436365655151</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <v>-8.424078095265429e-05</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>0.00027192978722001722</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="1">
         <v>0.00033081140110419877</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="1">
         <v>-3.6197568402529436e-05</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="1">
         <v>0.00010998602768836301</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="1">
         <v>0.00033638103677065652</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="1">
         <v>0.00075029447044723031</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="1">
         <v>0.00021726764560272185</v>
       </c>
-      <c r="O29">
+      <c r="O29" s="1">
         <v>0.0001621346262985713</v>
       </c>
-      <c r="P29">
+      <c r="P29" s="1">
         <v>-0.00034213009193165094</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" s="1">
         <v>-0.00023473282254862847</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="1">
         <v>-0.00018914576186804136</v>
       </c>
-      <c r="S29">
+      <c r="S29" s="1">
         <v>-0.00011969739202040137</v>
       </c>
-      <c r="T29">
+      <c r="T29" s="1">
         <v>0.00012872200597995842</v>
       </c>
-      <c r="U29">
+      <c r="U29" s="1">
         <v>-0.00016317819745507284</v>
       </c>
-      <c r="V29">
+      <c r="V29" s="1">
         <v>0.00022616507678797806</v>
       </c>
-      <c r="W29">
+      <c r="W29" s="1">
         <v>1.1019690382003326e-05</v>
       </c>
-      <c r="X29">
+      <c r="X29" s="1">
         <v>3.6771533621403145e-06</v>
       </c>
-      <c r="Y29">
+      <c r="Y29" s="1">
         <v>-0.00029123616327819376</v>
       </c>
-      <c r="Z29">
+      <c r="Z29" s="1">
         <v>0.0002345479464767585</v>
       </c>
-      <c r="AA29">
+      <c r="AA29" s="1">
         <v>-7.7534695720057932e-05</v>
       </c>
-      <c r="AB29">
+      <c r="AB29" s="1">
         <v>2.5075647193059804e-06</v>
       </c>
-      <c r="AC29">
+      <c r="AC29" s="1">
         <v>0.001250501091349832</v>
       </c>
-      <c r="AD29">
+      <c r="AD29" s="1">
         <v>0.0037848481119822776</v>
       </c>
-      <c r="AE29">
+      <c r="AE29" s="1">
         <v>0.0012534856450648042</v>
       </c>
-      <c r="AF29">
+      <c r="AF29" s="1">
         <v>0.0012362640354793126</v>
       </c>
-      <c r="AG29">
+      <c r="AG29" s="1">
         <v>0.0013178270498480297</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30">
+        <v>53</v>
+      </c>
+      <c r="B30" s="1">
         <v>0.0851819502540892</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="1">
         <v>-0.0083797414460541411</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="1">
         <v>-0.00035349287150833941</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="1">
         <v>5.6286347976563562e-06</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="1">
         <v>0.00025525825798129037</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <v>0.00029360963573863037</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>0.00044906228715563788</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="1">
         <v>0.00038317126559262935</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="1">
         <v>0.00024423981823125515</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="1">
         <v>5.3932431972644312e-06</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="1">
         <v>0.00036754751359776747</v>
       </c>
-      <c r="M30">
+      <c r="M30" s="1">
         <v>2.3064647196132781e-05</v>
       </c>
-      <c r="N30">
+      <c r="N30" s="1">
         <v>0.00057857216971576083</v>
       </c>
-      <c r="O30">
+      <c r="O30" s="1">
         <v>-0.00045972533415868756</v>
       </c>
-      <c r="P30">
+      <c r="P30" s="1">
         <v>0.0012066624855472099</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" s="1">
         <v>3.0478812118126452e-05</v>
       </c>
-      <c r="R30">
+      <c r="R30" s="1">
         <v>8.0643513947799284e-05</v>
       </c>
-      <c r="S30">
+      <c r="S30" s="1">
         <v>0.00018706677962094013</v>
       </c>
-      <c r="T30">
+      <c r="T30" s="1">
         <v>-1.4078523221663908e-05</v>
       </c>
-      <c r="U30">
+      <c r="U30" s="1">
         <v>0.00016773872132149051</v>
       </c>
-      <c r="V30">
+      <c r="V30" s="1">
         <v>-0.00046969471098306733</v>
       </c>
-      <c r="W30">
+      <c r="W30" s="1">
         <v>-9.1587472475258965e-06</v>
       </c>
-      <c r="X30">
+      <c r="X30" s="1">
         <v>4.6824994534044905e-05</v>
       </c>
-      <c r="Y30">
+      <c r="Y30" s="1">
         <v>-0.00063571416678490783</v>
       </c>
-      <c r="Z30">
+      <c r="Z30" s="1">
         <v>3.3703277798702064e-05</v>
       </c>
-      <c r="AA30">
+      <c r="AA30" s="1">
         <v>-0.00051872767693485504</v>
       </c>
-      <c r="AB30">
+      <c r="AB30" s="1">
         <v>1.6040497968779973e-05</v>
       </c>
-      <c r="AC30">
+      <c r="AC30" s="1">
         <v>0.0012776085422094516</v>
       </c>
-      <c r="AD30">
+      <c r="AD30" s="1">
         <v>0.0012534856450648042</v>
       </c>
-      <c r="AE30">
+      <c r="AE30" s="1">
         <v>0.0029401582177139445</v>
       </c>
-      <c r="AF30">
+      <c r="AF30" s="1">
         <v>0.0012414705941574922</v>
       </c>
-      <c r="AG30">
+      <c r="AG30" s="1">
         <v>0.0053990339389657655</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31">
+        <v>54</v>
+      </c>
+      <c r="B31" s="1">
         <v>0.081434628064292372</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="1">
         <v>-0.0073977080619296327</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="1">
         <v>-8.8866849927382162e-05</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="1">
         <v>1.2703278123123824e-06</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="1">
         <v>0.00021898721387131695</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="1">
         <v>0.00013859467638739837</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>0.00031826684568295248</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="1">
         <v>0.00045380117049193403</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="1">
         <v>-0.00017303076355890172</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="1">
         <v>5.0959898316985303e-05</v>
       </c>
-      <c r="L31">
+      <c r="L31" s="1">
         <v>0.00031564496351500375</v>
       </c>
-      <c r="M31">
+      <c r="M31" s="1">
         <v>0.00096389054516403936</v>
       </c>
-      <c r="N31">
+      <c r="N31" s="1">
         <v>-4.1682623424139581e-05</v>
       </c>
-      <c r="O31">
+      <c r="O31" s="1">
         <v>-0.000425978828580658</v>
       </c>
-      <c r="P31">
+      <c r="P31" s="1">
         <v>0.00014999868022961041</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" s="1">
         <v>-0.00012879468234123262</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="1">
         <v>-0.00010654230168147377</v>
       </c>
-      <c r="S31">
+      <c r="S31" s="1">
         <v>3.011872967537512e-05</v>
       </c>
-      <c r="T31">
+      <c r="T31" s="1">
         <v>2.8228823980311792e-05</v>
       </c>
-      <c r="U31">
+      <c r="U31" s="1">
         <v>-3.2514776949134919e-05</v>
       </c>
-      <c r="V31">
+      <c r="V31" s="1">
         <v>-9.070496986821622e-05</v>
       </c>
-      <c r="W31">
+      <c r="W31" s="1">
         <v>-3.1305119181720739e-05</v>
       </c>
-      <c r="X31">
+      <c r="X31" s="1">
         <v>1.6404632511981916e-05</v>
       </c>
-      <c r="Y31">
+      <c r="Y31" s="1">
         <v>1.2372478597373046e-05</v>
       </c>
-      <c r="Z31">
+      <c r="Z31" s="1">
         <v>-1.457645665327115e-05</v>
       </c>
-      <c r="AA31">
+      <c r="AA31" s="1">
         <v>-0.0001079307930026867</v>
       </c>
-      <c r="AB31">
+      <c r="AB31" s="1">
         <v>3.1776309221621492e-06</v>
       </c>
-      <c r="AC31">
+      <c r="AC31" s="1">
         <v>0.0012391383066635581</v>
       </c>
-      <c r="AD31">
+      <c r="AD31" s="1">
         <v>0.0012362640354793126</v>
       </c>
-      <c r="AE31">
+      <c r="AE31" s="1">
         <v>0.0012414705941574922</v>
       </c>
-      <c r="AF31">
+      <c r="AF31" s="1">
         <v>0.0018135803059644521</v>
       </c>
-      <c r="AG31">
+      <c r="AG31" s="1">
         <v>0.00013492181472514247</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32">
+        <v>55</v>
+      </c>
+      <c r="B32" s="1">
         <v>-5.2051663274334592</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="1">
         <v>-0.10376090035732416</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="1">
         <v>-0.015465113310734094</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="1">
         <v>0.00023431293734277461</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="1">
         <v>-0.051380044943535486</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="1">
         <v>-0.052309751881999156</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>-0.050744972872259708</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="1">
         <v>-0.051828397656293518</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="1">
         <v>0.00067060987598661047</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="1">
         <v>-0.0022862923980076057</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="1">
         <v>0.0041993662185908776</v>
       </c>
-      <c r="M32">
+      <c r="M32" s="1">
         <v>0.0010351810533156154</v>
       </c>
-      <c r="N32">
+      <c r="N32" s="1">
         <v>3.1580186061831977e-05</v>
       </c>
-      <c r="O32">
+      <c r="O32" s="1">
         <v>0.0091925838685297887</v>
       </c>
-      <c r="P32">
+      <c r="P32" s="1">
         <v>-0.0017516908652561412</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" s="1">
         <v>-0.002363346887545241</v>
       </c>
-      <c r="R32">
+      <c r="R32" s="1">
         <v>-0.0027763280727496724</v>
       </c>
-      <c r="S32">
+      <c r="S32" s="1">
         <v>-0.0037696055064498375</v>
       </c>
-      <c r="T32">
+      <c r="T32" s="1">
         <v>0.0023197227136744353</v>
       </c>
-      <c r="U32">
+      <c r="U32" s="1">
         <v>-0.00023464117456450375</v>
       </c>
-      <c r="V32">
+      <c r="V32" s="1">
         <v>-0.011344599918700774</v>
       </c>
-      <c r="W32">
+      <c r="W32" s="1">
         <v>0.0024175160597806871</v>
       </c>
-      <c r="X32">
+      <c r="X32" s="1">
         <v>-0.0018532857615941927</v>
       </c>
-      <c r="Y32">
+      <c r="Y32" s="1">
         <v>-0.01599702719363004</v>
       </c>
-      <c r="Z32">
+      <c r="Z32" s="1">
         <v>-0.0030273463646026495</v>
       </c>
-      <c r="AA32">
+      <c r="AA32" s="1">
         <v>-0.013075581650972921</v>
       </c>
-      <c r="AB32">
+      <c r="AB32" s="1">
         <v>0.00039927625109577281</v>
       </c>
-      <c r="AC32">
+      <c r="AC32" s="1">
         <v>0.0013246249422361656</v>
       </c>
-      <c r="AD32">
+      <c r="AD32" s="1">
         <v>0.0013178270498480297</v>
       </c>
-      <c r="AE32">
+      <c r="AE32" s="1">
         <v>0.0053990339389657655</v>
       </c>
-      <c r="AF32">
+      <c r="AF32" s="1">
         <v>0.00013492181472514247</v>
       </c>
-      <c r="AG32">
+      <c r="AG32" s="1">
         <v>0.48516565619882956</v>
       </c>
     </row>
